--- a/DASHBOARD1.xlsx
+++ b/DASHBOARD1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dragonnomada/Desktop/GitHub/scotiabank-excel-dashboards-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68117783-CA2F-C848-92D0-9C451CF022EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94D4D5F-7FC4-204E-BECA-5125FD49FCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="4" xr2:uid="{535DC7C3-8A8A-184D-A926-0931CED7ADA0}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16160" activeTab="4" xr2:uid="{535DC7C3-8A8A-184D-A926-0931CED7ADA0}"/>
   </bookViews>
   <sheets>
     <sheet name="factVentas" sheetId="5" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2326,7 +2326,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2436,56 +2436,16 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2501,11 +2461,7 @@
     <xf numFmtId="9" fontId="0" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="12" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="12" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
@@ -2523,6 +2479,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -55861,13 +55853,13 @@
       <c r="L19" s="1">
         <v>2023</v>
       </c>
-      <c r="M19" s="64">
+      <c r="M19" s="104">
         <v>2023</v>
       </c>
       <c r="N19" t="s">
         <v>23</v>
       </c>
-      <c r="O19" s="64">
+      <c r="O19" s="104">
         <v>2023</v>
       </c>
       <c r="P19" t="s">
@@ -55881,11 +55873,11 @@
       <c r="L20" s="1">
         <v>2024</v>
       </c>
-      <c r="M20" s="64"/>
+      <c r="M20" s="104"/>
       <c r="N20" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="64"/>
+      <c r="O20" s="104"/>
       <c r="P20" s="2" t="s">
         <v>29</v>
       </c>
@@ -55897,11 +55889,11 @@
       <c r="L21" s="1">
         <v>2025</v>
       </c>
-      <c r="M21" s="64"/>
+      <c r="M21" s="104"/>
       <c r="N21" t="s">
         <v>25</v>
       </c>
-      <c r="O21" s="64"/>
+      <c r="O21" s="104"/>
       <c r="P21" t="s">
         <v>30</v>
       </c>
@@ -55913,11 +55905,11 @@
       <c r="L22" s="9">
         <v>2026</v>
       </c>
-      <c r="M22" s="65"/>
+      <c r="M22" s="105"/>
       <c r="N22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O22" s="64"/>
+      <c r="O22" s="104"/>
       <c r="P22" s="2" t="s">
         <v>31</v>
       </c>
@@ -55926,7 +55918,7 @@
       </c>
     </row>
     <row r="23" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="O23" s="64"/>
+      <c r="O23" s="104"/>
       <c r="P23" t="s">
         <v>32</v>
       </c>
@@ -55935,7 +55927,7 @@
       </c>
     </row>
     <row r="24" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="O24" s="64"/>
+      <c r="O24" s="104"/>
       <c r="P24" s="2" t="s">
         <v>33</v>
       </c>
@@ -55944,13 +55936,13 @@
       </c>
     </row>
     <row r="25" spans="4:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="M25" s="64">
+      <c r="M25" s="104">
         <v>2024</v>
       </c>
       <c r="N25" t="s">
         <v>23</v>
       </c>
-      <c r="O25" s="64"/>
+      <c r="O25" s="104"/>
       <c r="P25" t="s">
         <v>34</v>
       </c>
@@ -55959,31 +55951,31 @@
       </c>
     </row>
     <row r="26" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="M26" s="64"/>
+      <c r="M26" s="104"/>
       <c r="N26" t="s">
         <v>24</v>
       </c>
-      <c r="O26" s="64"/>
+      <c r="O26" s="104"/>
       <c r="P26" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="M27" s="64"/>
+      <c r="M27" s="104"/>
       <c r="N27" t="s">
         <v>25</v>
       </c>
-      <c r="O27" s="64"/>
+      <c r="O27" s="104"/>
       <c r="P27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="28" spans="4:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="M28" s="65"/>
+      <c r="M28" s="105"/>
       <c r="N28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O28" s="64"/>
+      <c r="O28" s="104"/>
       <c r="P28" s="2" t="s">
         <v>37</v>
       </c>
@@ -55995,13 +55987,13 @@
       <c r="G29" t="s">
         <v>48</v>
       </c>
-      <c r="O29" s="64"/>
+      <c r="O29" s="104"/>
       <c r="P29" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="30" spans="4:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O30" s="65"/>
+      <c r="O30" s="105"/>
       <c r="P30" s="6" t="s">
         <v>39</v>
       </c>
@@ -56013,7 +56005,7 @@
       <c r="H31" t="s">
         <v>67</v>
       </c>
-      <c r="M31" s="64">
+      <c r="M31" s="104">
         <v>2025</v>
       </c>
       <c r="N31" t="s">
@@ -56027,7 +56019,7 @@
       <c r="H32" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="64"/>
+      <c r="M32" s="104"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -56039,11 +56031,11 @@
       <c r="H33" t="s">
         <v>69</v>
       </c>
-      <c r="M33" s="64"/>
+      <c r="M33" s="104"/>
       <c r="N33" t="s">
         <v>25</v>
       </c>
-      <c r="O33" s="64">
+      <c r="O33" s="104">
         <v>2024</v>
       </c>
       <c r="P33" t="s">
@@ -56051,23 +56043,23 @@
       </c>
     </row>
     <row r="34" spans="4:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="M34" s="65"/>
+      <c r="M34" s="105"/>
       <c r="N34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O34" s="64"/>
+      <c r="O34" s="104"/>
       <c r="P34" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="35" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="O35" s="64"/>
+      <c r="O35" s="104"/>
       <c r="P35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="O36" s="64"/>
+      <c r="O36" s="104"/>
       <c r="P36" s="2" t="s">
         <v>31</v>
       </c>
@@ -56079,23 +56071,23 @@
       <c r="G37" t="s">
         <v>71</v>
       </c>
-      <c r="M37" s="66">
+      <c r="M37" s="106">
         <v>2026</v>
       </c>
       <c r="N37" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="O37" s="64"/>
+      <c r="O37" s="104"/>
       <c r="P37" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="38" spans="4:17" x14ac:dyDescent="0.2">
-      <c r="M38" s="66"/>
+      <c r="M38" s="106"/>
       <c r="N38" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="O38" s="64"/>
+      <c r="O38" s="104"/>
       <c r="P38" s="2" t="s">
         <v>33</v>
       </c>
@@ -56104,21 +56096,21 @@
       <c r="E39" t="s">
         <v>72</v>
       </c>
-      <c r="M39" s="66"/>
+      <c r="M39" s="106"/>
       <c r="N39" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O39" s="64"/>
+      <c r="O39" s="104"/>
       <c r="P39" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="40" spans="4:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="M40" s="67"/>
+      <c r="M40" s="107"/>
       <c r="N40" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O40" s="64"/>
+      <c r="O40" s="104"/>
       <c r="P40" s="2" t="s">
         <v>35</v>
       </c>
@@ -56127,7 +56119,7 @@
       <c r="F41" t="s">
         <v>73</v>
       </c>
-      <c r="O41" s="64"/>
+      <c r="O41" s="104"/>
       <c r="P41" t="s">
         <v>36</v>
       </c>
@@ -56136,7 +56128,7 @@
       <c r="F42" t="s">
         <v>74</v>
       </c>
-      <c r="O42" s="64"/>
+      <c r="O42" s="104"/>
       <c r="P42" s="2" t="s">
         <v>37</v>
       </c>
@@ -56145,13 +56137,13 @@
       <c r="F43" t="s">
         <v>75</v>
       </c>
-      <c r="O43" s="64"/>
+      <c r="O43" s="104"/>
       <c r="P43" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="44" spans="4:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O44" s="65"/>
+      <c r="O44" s="105"/>
       <c r="P44" s="6" t="s">
         <v>39</v>
       </c>
@@ -56303,11 +56295,11 @@
       <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
       <c r="J2" s="33"/>
@@ -56315,9 +56307,9 @@
       <c r="L2" s="33"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
       <c r="H3" s="33"/>
       <c r="I3" s="34"/>
       <c r="J3" s="34" t="s">
@@ -56329,9 +56321,9 @@
       <c r="L3" s="33"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
       <c r="H4" s="33"/>
       <c r="I4" s="34" t="s">
         <v>78</v>
@@ -56345,9 +56337,9 @@
       <c r="L4" s="33"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="J5" s="33"/>
@@ -56369,11 +56361,11 @@
       <c r="G6" s="20"/>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
-      <c r="J6" s="61" t="s">
+      <c r="J6" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
       <c r="P6" t="s">
         <v>18</v>
       </c>
@@ -56480,11 +56472,11 @@
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="19"/>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
       <c r="K11" s="23" t="s">
         <v>84</v>
       </c>
@@ -56506,9 +56498,9 @@
         <v>121</v>
       </c>
       <c r="G12" s="19"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
       <c r="K12" s="23" t="s">
         <v>88</v>
       </c>
@@ -56550,11 +56542,11 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
-      <c r="K14" s="62">
+      <c r="K14" s="100">
         <f>K17-K18</f>
         <v>456000</v>
       </c>
-      <c r="L14" s="62"/>
+      <c r="L14" s="100"/>
       <c r="P14" t="s">
         <v>96</v>
       </c>
@@ -56738,11 +56730,11 @@
       <c r="H20" s="15"/>
       <c r="I20" s="28"/>
       <c r="J20" s="15"/>
-      <c r="K20" s="63">
+      <c r="K20" s="101">
         <f>K26-K14</f>
         <v>394520</v>
       </c>
-      <c r="L20" s="63"/>
+      <c r="L20" s="101"/>
     </row>
     <row r="21" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E21" s="15"/>
@@ -56855,11 +56847,11 @@
       <c r="H28" s="15"/>
       <c r="I28" s="28"/>
       <c r="J28" s="15"/>
-      <c r="K28" s="62">
+      <c r="K28" s="100">
         <f>K32/L31</f>
         <v>1812.0642474717429</v>
       </c>
-      <c r="L28" s="62"/>
+      <c r="L28" s="100"/>
     </row>
     <row r="29" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E29" s="15"/>
@@ -56948,11 +56940,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
       <c r="E3" s="45"/>
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
@@ -56960,39 +56952,39 @@
       <c r="I3" s="45"/>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="45"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111" t="s">
+      <c r="F4" s="93"/>
+      <c r="G4" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="H4" s="111" t="s">
+      <c r="H4" s="93" t="s">
         <v>105</v>
       </c>
       <c r="I4" s="45"/>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
       <c r="E5" s="45"/>
-      <c r="F5" s="111" t="s">
+      <c r="F5" s="93" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="14">
         <v>45658</v>
       </c>
       <c r="H5" s="14">
-        <v>45839</v>
+        <v>45748</v>
       </c>
       <c r="I5" s="45"/>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
       <c r="E6" s="45"/>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
@@ -57000,17 +56992,17 @@
       <c r="I6" s="45"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
-      <c r="N6" s="59" t="s">
+      <c r="N6" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="O6" s="59"/>
+      <c r="O6" s="103"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
-      <c r="R6" s="59" t="s">
+      <c r="R6" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="59"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B7" s="15"/>
@@ -57018,11 +57010,11 @@
       <c r="D7" s="20"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
       <c r="L7" s="15"/>
       <c r="M7" s="44" t="s">
         <v>77</v>
@@ -57090,32 +57082,32 @@
       </c>
       <c r="F9" s="21">
         <f>H5</f>
-        <v>45839</v>
+        <v>45748</v>
       </c>
       <c r="G9" s="26">
         <f>ROUNDUP(YEARFRAC(E9,F9), 1)</f>
-        <v>0.5</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="H9" s="27">
         <f>ROUNDUP(YEARFRAC(E9,F9) * 12, 1)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" s="26">
         <f>F9-E9</f>
-        <v>181</v>
-      </c>
-      <c r="L9" s="69">
+        <v>90</v>
+      </c>
+      <c r="L9" s="20">
         <v>2023</v>
       </c>
-      <c r="M9" s="70" cm="1">
+      <c r="M9" s="15" cm="1">
         <f t="array" ref="M9">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1))))</f>
         <v>2</v>
       </c>
-      <c r="N9" s="70" cm="1">
+      <c r="N9" s="15" cm="1">
         <f t="array" ref="N9">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1)))))</f>
         <v>2</v>
       </c>
-      <c r="O9" s="71">
+      <c r="O9" s="58">
         <f>N9/365</f>
         <v>5.4794520547945206E-3</v>
       </c>
@@ -57123,19 +57115,19 @@
         <f t="array" ref="P9">SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1))))</f>
         <v>14998</v>
       </c>
-      <c r="Q9" s="72" cm="1">
+      <c r="Q9" s="38" cm="1">
         <f t="array" ref="Q9">SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1)))) - P9</f>
         <v>8317.0800000000017</v>
       </c>
-      <c r="R9" s="73" cm="1">
+      <c r="R9" s="57" cm="1">
         <f t="array" ref="R9">AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1))))</f>
         <v>26</v>
       </c>
-      <c r="S9" s="72" cm="1">
+      <c r="S9" s="38" cm="1">
         <f t="array" ref="S9">SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE(L9, 1, 1)) * (factVentas[fecha] &lt; DATE(L9+1, 1, 1))))</f>
         <v>839.04</v>
       </c>
-      <c r="T9" s="72">
+      <c r="T9" s="38">
         <f>S9/M9</f>
         <v>419.52</v>
       </c>
@@ -57149,18 +57141,18 @@
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="L10" s="74">
+      <c r="L10" s="59">
         <v>2024</v>
       </c>
-      <c r="M10" s="75" cm="1">
+      <c r="M10" s="45" cm="1">
         <f t="array" ref="M10">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1))))</f>
         <v>74</v>
       </c>
-      <c r="N10" s="75" cm="1">
+      <c r="N10" s="45" cm="1">
         <f t="array" ref="N10">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1)))))</f>
         <v>58</v>
       </c>
-      <c r="O10" s="76">
+      <c r="O10" s="60">
         <f t="shared" ref="O10:O12" si="0">N10/365</f>
         <v>0.15890410958904111</v>
       </c>
@@ -57168,19 +57160,19 @@
         <f t="array" ref="P10">SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1))))</f>
         <v>432982</v>
       </c>
-      <c r="Q10" s="79" cm="1">
+      <c r="Q10" s="63" cm="1">
         <f t="array" ref="Q10">SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1)))) - P10</f>
         <v>308790.19999999995</v>
       </c>
-      <c r="R10" s="80" cm="1">
+      <c r="R10" s="64" cm="1">
         <f t="array" ref="R10">AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1))))</f>
         <v>27.135135135135137</v>
       </c>
-      <c r="S10" s="79" cm="1">
+      <c r="S10" s="63" cm="1">
         <f t="array" ref="S10">SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE(L10, 1, 1)) * (factVentas[fecha] &lt; DATE(L10+1, 1, 1))))</f>
         <v>26372.780000000006</v>
       </c>
-      <c r="T10" s="79">
+      <c r="T10" s="63">
         <f t="shared" ref="T10:T12" si="1">S10/M10</f>
         <v>356.38891891891899</v>
       </c>
@@ -57196,18 +57188,18 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
-      <c r="L11" s="69">
+      <c r="L11" s="20">
         <v>2025</v>
       </c>
-      <c r="M11" s="70" cm="1">
+      <c r="M11" s="15" cm="1">
         <f t="array" ref="M11">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1))))</f>
         <v>296</v>
       </c>
-      <c r="N11" s="70" cm="1">
+      <c r="N11" s="15" cm="1">
         <f t="array" ref="N11">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1)))))</f>
         <v>172</v>
       </c>
-      <c r="O11" s="71">
+      <c r="O11" s="58">
         <f t="shared" si="0"/>
         <v>0.47123287671232877</v>
       </c>
@@ -57215,19 +57207,19 @@
         <f t="array" ref="P11">SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1))))</f>
         <v>1380014.8</v>
       </c>
-      <c r="Q11" s="72" cm="1">
+      <c r="Q11" s="38" cm="1">
         <f t="array" ref="Q11">SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1)))) - P11</f>
         <v>1272270.7599999991</v>
       </c>
-      <c r="R11" s="73" cm="1">
+      <c r="R11" s="57" cm="1">
         <f t="array" ref="R11">AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1))))</f>
         <v>30.719594594594593</v>
       </c>
-      <c r="S11" s="72" cm="1">
+      <c r="S11" s="38" cm="1">
         <f t="array" ref="S11">SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE(L11, 1, 1)) * (factVentas[fecha] &lt; DATE(L11+1, 1, 1))))</f>
         <v>83958.330000000031</v>
       </c>
-      <c r="T11" s="72">
+      <c r="T11" s="38">
         <f t="shared" si="1"/>
         <v>283.64300675675685</v>
       </c>
@@ -57235,17 +57227,17 @@
     <row r="12" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
       <c r="G12" s="23" t="s">
         <v>84</v>
       </c>
       <c r="H12" s="25" cm="1">
         <f t="array" ref="H12">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha],(factVentas[fecha]&gt;=E9)*(factVentas[fecha]&lt;F9))))</f>
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>95</v>
@@ -57273,7 +57265,7 @@
         <f t="array" ref="Q12">SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE(L12, 1, 1)) * (factVentas[fecha] &lt; DATE(L12+1, 1, 1)))) - P12</f>
         <v>317044.8800000003</v>
       </c>
-      <c r="R12" s="78" cm="1">
+      <c r="R12" s="62" cm="1">
         <f t="array" ref="R12">AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE(L12, 1, 1)) * (factVentas[fecha] &lt; DATE(L12+1, 1, 1))))</f>
         <v>32.311688311688314</v>
       </c>
@@ -57291,19 +57283,19 @@
         <v>77</v>
       </c>
       <c r="C13" s="15"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
       <c r="G13" s="23" t="s">
         <v>88</v>
       </c>
       <c r="H13" s="36">
         <f>H12/I9</f>
-        <v>0.37016574585635359</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="27">
         <f>H13*7</f>
-        <v>2.5911602209944751</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="19">
@@ -57326,7 +57318,7 @@
         <f>SUM(Q9:Q12)</f>
         <v>1906422.9199999995</v>
       </c>
-      <c r="R13" s="81">
+      <c r="R13" s="65">
         <f>AVERAGE(R9:R12)</f>
         <v>29.04160451035451</v>
       </c>
@@ -57342,7 +57334,7 @@
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" s="35" cm="1">
         <f t="array" ref="B14">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="19"/>
@@ -57361,11 +57353,11 @@
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
-      <c r="H15" s="62">
+      <c r="H15" s="100">
         <f>H18-H19</f>
-        <v>522988.4</v>
-      </c>
-      <c r="I15" s="62"/>
+        <v>171360</v>
+      </c>
+      <c r="I15" s="100"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B16" s="15"/>
@@ -57379,17 +57371,17 @@
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
-      <c r="N16" s="59" t="s">
+      <c r="N16" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="O16" s="59"/>
+      <c r="O16" s="103"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
-      <c r="R16" s="59" t="s">
+      <c r="R16" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="S16" s="59"/>
-      <c r="T16" s="59"/>
+      <c r="S16" s="103"/>
+      <c r="T16" s="103"/>
       <c r="U16" s="45"/>
       <c r="V16" s="45"/>
       <c r="W16" s="45"/>
@@ -57434,7 +57426,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="45"/>
-      <c r="V17" s="113" t="s">
+      <c r="V17" s="95" t="s">
         <v>675</v>
       </c>
       <c r="W17" s="45"/>
@@ -57450,11 +57442,11 @@
       <c r="G18" s="15"/>
       <c r="H18" s="30" cm="1">
         <f t="array" ref="H18">SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>614174</v>
+        <v>194859</v>
       </c>
       <c r="I18" s="30">
         <f>H18/B14</f>
-        <v>6080.9306930693074</v>
+        <v>7794.36</v>
       </c>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
@@ -57467,7 +57459,7 @@
       <c r="S18" s="15"/>
       <c r="T18" s="15"/>
       <c r="U18" s="45"/>
-      <c r="V18" s="112" t="s">
+      <c r="V18" s="94" t="s">
         <v>28</v>
       </c>
       <c r="W18" s="45"/>
@@ -57483,11 +57475,11 @@
       <c r="G19" s="15"/>
       <c r="H19" s="30" cm="1">
         <f t="array" ref="H19">SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>91185.600000000006</v>
+        <v>23499</v>
       </c>
       <c r="I19" s="30">
         <f>H19/B14</f>
-        <v>902.8277227722773</v>
+        <v>939.96</v>
       </c>
       <c r="K19" s="54">
         <v>2023</v>
@@ -57499,11 +57491,11 @@
         <f t="array" ref="M19">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$19,MATCH(L19,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$19,MATCH(L19,$V$18:$V$29,0) + 1,1))))</f>
         <v>2</v>
       </c>
-      <c r="N19" s="82" cm="1">
+      <c r="N19" s="66" cm="1">
         <f t="array" ref="N19">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$19,MATCH(L19,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$19,MATCH(L19,$V$18:$V$29,0) + 1,1)))))</f>
         <v>2</v>
       </c>
-      <c r="O19" s="84">
+      <c r="O19" s="68">
         <f>N19/(DATE($K$19,MATCH(L19,$V$18:$V$29,0) + 1,1)-DATE($K$19,MATCH(L19,$V$18:$V$29,0),1))</f>
         <v>6.4516129032258063E-2</v>
       </c>
@@ -57515,7 +57507,7 @@
         <f t="array" ref="Q19">SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$19,MATCH(L19,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$19,MATCH(L19,$V$18:$V$29,0) + 1,1)))) - P19</f>
         <v>8317.0800000000017</v>
       </c>
-      <c r="R19" s="77" cm="1">
+      <c r="R19" s="61" cm="1">
         <f t="array" ref="R19">AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$19,MATCH(L19,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$19,MATCH(L19,$V$18:$V$29,0) + 1,1))))</f>
         <v>26</v>
       </c>
@@ -57523,12 +57515,12 @@
         <f t="array" ref="S19">SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$19,MATCH(L19,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$19,MATCH(L19,$V$18:$V$29,0) + 1,1))))</f>
         <v>839.04</v>
       </c>
-      <c r="T19" s="86">
+      <c r="T19" s="70">
         <f>S19 / M19</f>
         <v>419.52</v>
       </c>
       <c r="U19" s="45"/>
-      <c r="V19" s="112" t="s">
+      <c r="V19" s="94" t="s">
         <v>29</v>
       </c>
       <c r="W19" s="45"/>
@@ -57544,15 +57536,15 @@
       <c r="I20" s="16"/>
       <c r="K20" s="19"/>
       <c r="L20" s="15"/>
-      <c r="M20" s="105">
+      <c r="M20" s="87">
         <f>SUM(M19)</f>
         <v>2</v>
       </c>
-      <c r="N20" s="103">
+      <c r="N20" s="85">
         <f>AVERAGE(N19)</f>
         <v>2</v>
       </c>
-      <c r="O20" s="102">
+      <c r="O20" s="84">
         <f>AVERAGE(O19)</f>
         <v>6.4516129032258063E-2</v>
       </c>
@@ -57560,11 +57552,11 @@
         <f>SUM(P19)</f>
         <v>14998</v>
       </c>
-      <c r="Q20" s="104">
+      <c r="Q20" s="86">
         <f>SUM(Q19)</f>
         <v>8317.0800000000017</v>
       </c>
-      <c r="R20" s="81">
+      <c r="R20" s="65">
         <f>AVERAGE(R19)</f>
         <v>26</v>
       </c>
@@ -57577,7 +57569,7 @@
         <v>419.52</v>
       </c>
       <c r="U20" s="45"/>
-      <c r="V20" s="112" t="s">
+      <c r="V20" s="94" t="s">
         <v>30</v>
       </c>
       <c r="W20" s="45"/>
@@ -57591,23 +57583,23 @@
       <c r="E21" s="15"/>
       <c r="F21" s="28"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="63">
+      <c r="H21" s="101">
         <f>H27-H15</f>
-        <v>422866.42000000004</v>
-      </c>
-      <c r="I21" s="63"/>
+        <v>109828.80000000005</v>
+      </c>
+      <c r="I21" s="101"/>
       <c r="K21" s="19"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="85"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="69"/>
       <c r="P21" s="38"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="68"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="57"/>
       <c r="S21" s="38"/>
-      <c r="T21" s="87"/>
+      <c r="T21" s="71"/>
       <c r="U21" s="45"/>
-      <c r="V21" s="112" t="s">
+      <c r="V21" s="94" t="s">
         <v>31</v>
       </c>
       <c r="W21" s="45"/>
@@ -57624,22 +57616,22 @@
       <c r="K22" s="96">
         <v>2024</v>
       </c>
-      <c r="L22" s="70" t="s">
+      <c r="L22" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="M22" s="70" cm="1">
+      <c r="M22" s="15" cm="1">
         <f t="array" ref="M22">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L22,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1))))</f>
         <v>0</v>
       </c>
-      <c r="N22" s="97" cm="1">
+      <c r="N22" s="67" cm="1">
         <f t="array" ref="N22">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L22,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)))))</f>
         <v>0</v>
       </c>
-      <c r="O22" s="85">
-        <f>N22/(DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L22,$V$18:$V$29,0),1))</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="72" t="str" cm="1">
+      <c r="O22" s="69">
+        <f t="shared" ref="O22:O33" si="2">N22/(DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L22,$V$18:$V$29,0),1))</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="38" t="str" cm="1">
         <f t="array" ref="P22">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L22,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L22,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v/>
       </c>
@@ -57647,7 +57639,7 @@
         <f t="array" ref="Q22">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L22,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)))) - P22,"")</f>
         <v/>
       </c>
-      <c r="R22" s="73" t="str" cm="1">
+      <c r="R22" s="57" t="str" cm="1">
         <f t="array" ref="R22">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L22,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v/>
       </c>
@@ -57655,12 +57647,12 @@
         <f t="array" ref="S22">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L22,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L22,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v/>
       </c>
-      <c r="T22" s="87" t="str">
+      <c r="T22" s="71" t="str">
         <f>IFERROR(S22 / M22,"")</f>
         <v/>
       </c>
       <c r="U22" s="45"/>
-      <c r="V22" s="112" t="s">
+      <c r="V22" s="94" t="s">
         <v>32</v>
       </c>
       <c r="W22" s="45"/>
@@ -57679,22 +57671,22 @@
         <v>100</v>
       </c>
       <c r="K23" s="96"/>
-      <c r="L23" s="75" t="s">
+      <c r="L23" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="M23" s="75" cm="1">
+      <c r="M23" s="45" cm="1">
         <f t="array" ref="M23">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L23,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1))))</f>
         <v>5</v>
       </c>
-      <c r="N23" s="98" cm="1">
+      <c r="N23" s="80" cm="1">
         <f t="array" ref="N23">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L23,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)))))</f>
         <v>5</v>
       </c>
-      <c r="O23" s="92">
-        <f>N23/(DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L23,$V$18:$V$29,0),1))</f>
+      <c r="O23" s="76">
+        <f t="shared" si="2"/>
         <v>0.17241379310344829</v>
       </c>
-      <c r="P23" s="79" cm="1">
+      <c r="P23" s="63" cm="1">
         <f t="array" ref="P23">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L23,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L23,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>26449</v>
       </c>
@@ -57702,7 +57694,7 @@
         <f t="array" ref="Q23">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L23,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)))) - P23,"")</f>
         <v>15845.5</v>
       </c>
-      <c r="R23" s="80" cm="1">
+      <c r="R23" s="64" cm="1">
         <f t="array" ref="R23">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L23,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>22.2</v>
       </c>
@@ -57710,12 +57702,12 @@
         <f t="array" ref="S23">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L23,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L23,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>1909.38</v>
       </c>
-      <c r="T23" s="88">
-        <f t="shared" ref="T23:T33" si="2">IFERROR(S23 / M23,"")</f>
+      <c r="T23" s="72">
+        <f t="shared" ref="T23:T33" si="3">IFERROR(S23 / M23,"")</f>
         <v>381.87600000000003</v>
       </c>
       <c r="U23" s="45"/>
-      <c r="V23" s="112" t="s">
+      <c r="V23" s="94" t="s">
         <v>33</v>
       </c>
       <c r="W23" s="45"/>
@@ -57731,29 +57723,29 @@
       <c r="G24" s="15"/>
       <c r="H24" s="31" cm="1">
         <f t="array" ref="H24">SUM(_xlfn._xlws.FILTER(factVentas[monto], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>522988.4</v>
+        <v>171360</v>
       </c>
       <c r="I24" s="31">
         <f>H24/B14</f>
-        <v>5178.10297029703</v>
+        <v>6854.4</v>
       </c>
       <c r="K24" s="96"/>
-      <c r="L24" s="70" t="s">
+      <c r="L24" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="M24" s="70" cm="1">
+      <c r="M24" s="15" cm="1">
         <f t="array" ref="M24">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L24,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1))))</f>
         <v>4</v>
       </c>
-      <c r="N24" s="97" cm="1">
+      <c r="N24" s="67" cm="1">
         <f t="array" ref="N24">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L24,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)))))</f>
         <v>4</v>
       </c>
-      <c r="O24" s="85">
-        <f>N24/(DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L24,$V$18:$V$29,0),1))</f>
+      <c r="O24" s="69">
+        <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="P24" s="72" cm="1">
+      <c r="P24" s="38" cm="1">
         <f t="array" ref="P24">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L24,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L24,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>22900</v>
       </c>
@@ -57761,7 +57753,7 @@
         <f t="array" ref="Q24">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L24,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)))) - P24,"")</f>
         <v>23226</v>
       </c>
-      <c r="R24" s="73" cm="1">
+      <c r="R24" s="57" cm="1">
         <f t="array" ref="R24">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L24,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>27.5</v>
       </c>
@@ -57769,12 +57761,12 @@
         <f t="array" ref="S24">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L24,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L24,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>1556.61</v>
       </c>
-      <c r="T24" s="87">
-        <f t="shared" si="2"/>
+      <c r="T24" s="71">
+        <f t="shared" si="3"/>
         <v>389.15249999999997</v>
       </c>
       <c r="U24" s="45"/>
-      <c r="V24" s="112" t="s">
+      <c r="V24" s="94" t="s">
         <v>34</v>
       </c>
       <c r="W24" s="45"/>
@@ -57790,29 +57782,29 @@
       <c r="G25" s="15"/>
       <c r="H25" s="32">
         <f>H26/H24</f>
-        <v>1.6342030148278623</v>
+        <v>1.5037920168067227</v>
       </c>
       <c r="I25" s="32" cm="1">
         <f t="array" ref="I25">AVERAGE(_xlfn._xlws.FILTER(factVentas[interes], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>1.7592452079207923</v>
+        <v>1.6679999999999995</v>
       </c>
       <c r="K25" s="96"/>
-      <c r="L25" s="75" t="s">
+      <c r="L25" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="M25" s="75" cm="1">
+      <c r="M25" s="45" cm="1">
         <f t="array" ref="M25">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L25,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1))))</f>
         <v>5</v>
       </c>
-      <c r="N25" s="98" cm="1">
+      <c r="N25" s="80" cm="1">
         <f t="array" ref="N25">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L25,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)))))</f>
         <v>4</v>
       </c>
-      <c r="O25" s="92">
-        <f>N25/(DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L25,$V$18:$V$29,0),1))</f>
+      <c r="O25" s="76">
+        <f t="shared" si="2"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="P25" s="79" cm="1">
+      <c r="P25" s="63" cm="1">
         <f t="array" ref="P25">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L25,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L25,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>24199</v>
       </c>
@@ -57820,7 +57812,7 @@
         <f t="array" ref="Q25">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L25,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)))) - P25,"")</f>
         <v>16887.5</v>
       </c>
-      <c r="R25" s="80" cm="1">
+      <c r="R25" s="64" cm="1">
         <f t="array" ref="R25">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L25,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>22.6</v>
       </c>
@@ -57828,12 +57820,12 @@
         <f t="array" ref="S25">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L25,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L25,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>1641.13</v>
       </c>
-      <c r="T25" s="88">
-        <f t="shared" si="2"/>
+      <c r="T25" s="72">
+        <f t="shared" si="3"/>
         <v>328.226</v>
       </c>
       <c r="U25" s="45"/>
-      <c r="V25" s="112" t="s">
+      <c r="V25" s="94" t="s">
         <v>35</v>
       </c>
       <c r="W25" s="45"/>
@@ -57849,29 +57841,29 @@
       <c r="G26" s="15"/>
       <c r="H26" s="31" cm="1">
         <f t="array" ref="H26">SUM(_xlfn._xlws.FILTER(factVentas[subtotal], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>854669.22000000009</v>
+        <v>257689.80000000002</v>
       </c>
       <c r="I26" s="31">
         <f>H26/B14</f>
-        <v>8462.0714851485154</v>
+        <v>10307.592000000001</v>
       </c>
       <c r="K26" s="96"/>
-      <c r="L26" s="70" t="s">
+      <c r="L26" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M26" s="70" cm="1">
+      <c r="M26" s="15" cm="1">
         <f t="array" ref="M26">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L26,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1))))</f>
         <v>7</v>
       </c>
-      <c r="N26" s="97" cm="1">
+      <c r="N26" s="67" cm="1">
         <f t="array" ref="N26">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L26,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)))))</f>
         <v>6</v>
       </c>
-      <c r="O26" s="85">
-        <f>N26/(DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L26,$V$18:$V$29,0),1))</f>
+      <c r="O26" s="69">
+        <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="P26" s="72" cm="1">
+      <c r="P26" s="38" cm="1">
         <f t="array" ref="P26">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L26,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L26,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>35996</v>
       </c>
@@ -57879,7 +57871,7 @@
         <f t="array" ref="Q26">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L26,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)))) - P26,"")</f>
         <v>20615.399999999994</v>
       </c>
-      <c r="R26" s="73" cm="1">
+      <c r="R26" s="57" cm="1">
         <f t="array" ref="R26">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L26,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>23</v>
       </c>
@@ -57887,12 +57879,12 @@
         <f t="array" ref="S26">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L26,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L26,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>2486.65</v>
       </c>
-      <c r="T26" s="87">
-        <f t="shared" si="2"/>
+      <c r="T26" s="71">
+        <f t="shared" si="3"/>
         <v>355.23571428571432</v>
       </c>
       <c r="U26" s="45"/>
-      <c r="V26" s="112" t="s">
+      <c r="V26" s="94" t="s">
         <v>36</v>
       </c>
       <c r="W26" s="45"/>
@@ -57908,29 +57900,29 @@
       <c r="G27" s="15"/>
       <c r="H27" s="31" cm="1">
         <f t="array" ref="H27">SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>945854.82000000007</v>
+        <v>281188.80000000005</v>
       </c>
       <c r="I27" s="31">
         <f>H27/B14</f>
-        <v>9364.8992079207928</v>
+        <v>11247.552000000001</v>
       </c>
       <c r="K27" s="96"/>
-      <c r="L27" s="75" t="s">
+      <c r="L27" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="75" cm="1">
+      <c r="M27" s="45" cm="1">
         <f t="array" ref="M27">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L27,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1))))</f>
         <v>11</v>
       </c>
-      <c r="N27" s="98" cm="1">
+      <c r="N27" s="80" cm="1">
         <f t="array" ref="N27">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L27,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)))))</f>
         <v>7</v>
       </c>
-      <c r="O27" s="92">
-        <f>N27/(DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L27,$V$18:$V$29,0),1))</f>
+      <c r="O27" s="76">
+        <f t="shared" si="2"/>
         <v>0.23333333333333334</v>
       </c>
-      <c r="P27" s="79" cm="1">
+      <c r="P27" s="63" cm="1">
         <f t="array" ref="P27">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L27,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L27,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>64236</v>
       </c>
@@ -57938,7 +57930,7 @@
         <f t="array" ref="Q27">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L27,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)))) - P27,"")</f>
         <v>32495.5</v>
       </c>
-      <c r="R27" s="80" cm="1">
+      <c r="R27" s="64" cm="1">
         <f t="array" ref="R27">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L27,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>23.181818181818183</v>
       </c>
@@ -57946,12 +57938,12 @@
         <f t="array" ref="S27">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L27,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L27,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>3866.7699999999995</v>
       </c>
-      <c r="T27" s="88">
-        <f t="shared" si="2"/>
+      <c r="T27" s="72">
+        <f t="shared" si="3"/>
         <v>351.52454545454543</v>
       </c>
       <c r="U27" s="45"/>
-      <c r="V27" s="112" t="s">
+      <c r="V27" s="94" t="s">
         <v>37</v>
       </c>
       <c r="W27" s="45"/>
@@ -57966,22 +57958,22 @@
       <c r="H28" s="16"/>
       <c r="I28" s="16"/>
       <c r="K28" s="96"/>
-      <c r="L28" s="70" t="s">
+      <c r="L28" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="M28" s="70" cm="1">
+      <c r="M28" s="15" cm="1">
         <f t="array" ref="M28">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L28,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1))))</f>
         <v>9</v>
       </c>
-      <c r="N28" s="97" cm="1">
+      <c r="N28" s="67" cm="1">
         <f t="array" ref="N28">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L28,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)))))</f>
         <v>8</v>
       </c>
-      <c r="O28" s="85">
-        <f>N28/(DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L28,$V$18:$V$29,0),1))</f>
+      <c r="O28" s="69">
+        <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="P28" s="72" cm="1">
+      <c r="P28" s="38" cm="1">
         <f t="array" ref="P28">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L28,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L28,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>56698</v>
       </c>
@@ -57989,7 +57981,7 @@
         <f t="array" ref="Q28">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L28,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)))) - P28,"")</f>
         <v>62847</v>
       </c>
-      <c r="R28" s="73" cm="1">
+      <c r="R28" s="57" cm="1">
         <f t="array" ref="R28">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L28,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>32.555555555555557</v>
       </c>
@@ -57997,12 +57989,12 @@
         <f t="array" ref="S28">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L28,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L28,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>3232.83</v>
       </c>
-      <c r="T28" s="87">
-        <f t="shared" si="2"/>
+      <c r="T28" s="71">
+        <f t="shared" si="3"/>
         <v>359.20333333333332</v>
       </c>
       <c r="U28" s="45"/>
-      <c r="V28" s="112" t="s">
+      <c r="V28" s="94" t="s">
         <v>38</v>
       </c>
       <c r="W28" s="45"/>
@@ -58016,28 +58008,28 @@
       <c r="E29" s="15"/>
       <c r="F29" s="28"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="62">
+      <c r="H29" s="100">
         <f>H21/I32</f>
-        <v>13194.163861600249</v>
-      </c>
-      <c r="I29" s="62"/>
+        <v>3524.6726572528896</v>
+      </c>
+      <c r="I29" s="100"/>
       <c r="K29" s="96"/>
-      <c r="L29" s="75" t="s">
+      <c r="L29" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="M29" s="75" cm="1">
+      <c r="M29" s="45" cm="1">
         <f t="array" ref="M29">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L29,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1))))</f>
         <v>19</v>
       </c>
-      <c r="N29" s="98" cm="1">
+      <c r="N29" s="80" cm="1">
         <f t="array" ref="N29">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L29,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)))))</f>
         <v>14</v>
       </c>
-      <c r="O29" s="92">
-        <f>N29/(DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L29,$V$18:$V$29,0),1))</f>
+      <c r="O29" s="76">
+        <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="P29" s="79" cm="1">
+      <c r="P29" s="63" cm="1">
         <f t="array" ref="P29">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L29,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L29,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>86930</v>
       </c>
@@ -58045,7 +58037,7 @@
         <f t="array" ref="Q29">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L29,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)))) - P29,"")</f>
         <v>85330.199999999983</v>
       </c>
-      <c r="R29" s="80" cm="1">
+      <c r="R29" s="64" cm="1">
         <f t="array" ref="R29">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L29,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>30.894736842105264</v>
       </c>
@@ -58053,12 +58045,12 @@
         <f t="array" ref="S29">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L29,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L29,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>5516.7699999999995</v>
       </c>
-      <c r="T29" s="88">
-        <f t="shared" si="2"/>
+      <c r="T29" s="72">
+        <f t="shared" si="3"/>
         <v>290.35631578947368</v>
       </c>
       <c r="U29" s="45"/>
-      <c r="V29" s="112" t="s">
+      <c r="V29" s="94" t="s">
         <v>39</v>
       </c>
       <c r="W29" s="45"/>
@@ -58073,22 +58065,22 @@
       <c r="H30" s="16"/>
       <c r="I30" s="16"/>
       <c r="K30" s="96"/>
-      <c r="L30" s="70" t="s">
+      <c r="L30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M30" s="70" cm="1">
+      <c r="M30" s="15" cm="1">
         <f t="array" ref="M30">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L30,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1))))</f>
         <v>7</v>
       </c>
-      <c r="N30" s="97" cm="1">
+      <c r="N30" s="67" cm="1">
         <f t="array" ref="N30">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L30,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)))))</f>
         <v>4</v>
       </c>
-      <c r="O30" s="85">
-        <f>N30/(DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L30,$V$18:$V$29,0),1))</f>
+      <c r="O30" s="69">
+        <f t="shared" si="2"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="P30" s="72" cm="1">
+      <c r="P30" s="38" cm="1">
         <f t="array" ref="P30">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L30,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L30,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>73977</v>
       </c>
@@ -58096,7 +58088,7 @@
         <f t="array" ref="Q30">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L30,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)))) - P30,"")</f>
         <v>30567.100000000006</v>
       </c>
-      <c r="R30" s="73" cm="1">
+      <c r="R30" s="57" cm="1">
         <f t="array" ref="R30">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L30,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>27.714285714285715</v>
       </c>
@@ -58104,8 +58096,8 @@
         <f t="array" ref="S30">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L30,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L30,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>4044.1299999999997</v>
       </c>
-      <c r="T30" s="87">
-        <f t="shared" si="2"/>
+      <c r="T30" s="71">
+        <f t="shared" si="3"/>
         <v>577.73285714285714</v>
       </c>
       <c r="U30" s="45"/>
@@ -58126,22 +58118,22 @@
         <v>100</v>
       </c>
       <c r="K31" s="96"/>
-      <c r="L31" s="75" t="s">
+      <c r="L31" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="M31" s="75" cm="1">
+      <c r="M31" s="45" cm="1">
         <f t="array" ref="M31">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L31,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1))))</f>
         <v>0</v>
       </c>
-      <c r="N31" s="98" cm="1">
+      <c r="N31" s="80" cm="1">
         <f t="array" ref="N31">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L31,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)))))</f>
         <v>0</v>
       </c>
-      <c r="O31" s="92">
-        <f>N31/(DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L31,$V$18:$V$29,0),1))</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="79" t="str" cm="1">
+      <c r="O31" s="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="63" t="str" cm="1">
         <f t="array" ref="P31">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L31,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L31,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v/>
       </c>
@@ -58149,7 +58141,7 @@
         <f t="array" ref="Q31">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L31,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)))) - P31,"")</f>
         <v/>
       </c>
-      <c r="R31" s="80" t="str" cm="1">
+      <c r="R31" s="64" t="str" cm="1">
         <f t="array" ref="R31">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L31,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v/>
       </c>
@@ -58157,8 +58149,8 @@
         <f t="array" ref="S31">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L31,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L31,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v/>
       </c>
-      <c r="T31" s="88" t="str">
-        <f t="shared" si="2"/>
+      <c r="T31" s="72" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U31" s="45"/>
@@ -58177,25 +58169,25 @@
       <c r="H32" s="31"/>
       <c r="I32" s="56" cm="1">
         <f t="array" ref="I32">AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>32.049504950495049</v>
+        <v>31.16</v>
       </c>
       <c r="K32" s="96"/>
-      <c r="L32" s="70" t="s">
+      <c r="L32" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="M32" s="70" cm="1">
+      <c r="M32" s="15" cm="1">
         <f t="array" ref="M32">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L32,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1))))</f>
         <v>3</v>
       </c>
-      <c r="N32" s="97" cm="1">
+      <c r="N32" s="67" cm="1">
         <f t="array" ref="N32">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L32,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)))))</f>
         <v>3</v>
       </c>
-      <c r="O32" s="85">
-        <f>N32/(DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L32,$V$18:$V$29,0),1))</f>
+      <c r="O32" s="69">
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="P32" s="72" cm="1">
+      <c r="P32" s="38" cm="1">
         <f t="array" ref="P32">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L32,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L32,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>19899</v>
       </c>
@@ -58203,7 +58195,7 @@
         <f t="array" ref="Q32">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L32,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)))) - P32,"")</f>
         <v>14818</v>
       </c>
-      <c r="R32" s="73" cm="1">
+      <c r="R32" s="57" cm="1">
         <f t="array" ref="R32">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L32,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>32.666666666666664</v>
       </c>
@@ -58211,8 +58203,8 @@
         <f t="array" ref="S32">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L32,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L32,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>963.23</v>
       </c>
-      <c r="T32" s="87">
-        <f t="shared" si="2"/>
+      <c r="T32" s="71">
+        <f t="shared" si="3"/>
         <v>321.07666666666665</v>
       </c>
       <c r="U32" s="45"/>
@@ -58230,13 +58222,13 @@
       <c r="G33" s="15"/>
       <c r="H33" s="31" cm="1">
         <f t="array" ref="H33">SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= E9) * (factVentas[fecha] &lt; F9)))</f>
-        <v>28169.920000000006</v>
+        <v>8318.98</v>
       </c>
       <c r="I33" s="31">
         <f>H33/B14</f>
-        <v>278.91009900990105</v>
-      </c>
-      <c r="K33" s="57"/>
+        <v>332.75919999999996</v>
+      </c>
+      <c r="K33" s="97"/>
       <c r="L33" s="47" t="s">
         <v>39</v>
       </c>
@@ -58244,12 +58236,12 @@
         <f t="array" ref="M33">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L33,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L33,$V$18:$V$29,0) + 1,1))))</f>
         <v>4</v>
       </c>
-      <c r="N33" s="91" cm="1">
+      <c r="N33" s="75" cm="1">
         <f t="array" ref="N33">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$22,MATCH(L33,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$22,MATCH(L33,$V$18:$V$29,0) + 1,1)))))</f>
         <v>3</v>
       </c>
-      <c r="O33" s="93">
-        <f>N33/(DATE($K$22,MATCH(L33,$V$18:$V$29,0) + 1,1)-DATE($K$22,MATCH(L33,$V$18:$V$29,0),1))</f>
+      <c r="O33" s="77">
+        <f t="shared" si="2"/>
         <v>9.6774193548387094E-2</v>
       </c>
       <c r="P33" s="49" cm="1">
@@ -58260,7 +58252,7 @@
         <f t="array" ref="Q33">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L33,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L33,$V$18:$V$29,0) + 1,1)))) - P33,"")</f>
         <v>6158</v>
       </c>
-      <c r="R33" s="78" cm="1">
+      <c r="R33" s="62" cm="1">
         <f t="array" ref="R33">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L33,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L33,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>21.5</v>
       </c>
@@ -58268,8 +58260,8 @@
         <f t="array" ref="S33">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$22,MATCH(L33,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$22,MATCH(L33,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>1155.28</v>
       </c>
-      <c r="T33" s="89">
-        <f t="shared" si="2"/>
+      <c r="T33" s="73">
+        <f t="shared" si="3"/>
         <v>288.82</v>
       </c>
       <c r="U33" s="45"/>
@@ -58279,15 +58271,15 @@
     <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="K34" s="19"/>
       <c r="L34" s="15"/>
-      <c r="M34" s="105">
+      <c r="M34" s="87">
         <f>SUM(M22:M33)</f>
         <v>74</v>
       </c>
-      <c r="N34" s="81">
+      <c r="N34" s="65">
         <f>AVERAGE(N22:N33)</f>
         <v>4.833333333333333</v>
       </c>
-      <c r="O34" s="102">
+      <c r="O34" s="84">
         <f>AVERAGE(O22:O33)</f>
         <v>0.15845383759733037</v>
       </c>
@@ -58296,19 +58288,19 @@
         <v>432982</v>
       </c>
       <c r="Q34" s="43">
-        <f t="shared" ref="Q34" si="3">SUM(Q22:Q33)</f>
+        <f t="shared" ref="Q34" si="4">SUM(Q22:Q33)</f>
         <v>308790.19999999995</v>
       </c>
-      <c r="R34" s="81">
+      <c r="R34" s="65">
         <f>AVERAGE(R22:R33)</f>
         <v>26.381306296043135</v>
       </c>
       <c r="S34" s="43">
-        <f t="shared" ref="S34:T34" si="4">AVERAGE(S22:S33)</f>
+        <f t="shared" ref="S34:T34" si="5">AVERAGE(S22:S33)</f>
         <v>2637.2779999999998</v>
       </c>
       <c r="T34" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>364.32039326725908</v>
       </c>
       <c r="U34" s="45"/>
@@ -58319,13 +58311,13 @@
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
       <c r="M35" s="15"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="94"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="78"/>
       <c r="P35" s="15"/>
-      <c r="Q35" s="95"/>
-      <c r="R35" s="68"/>
+      <c r="Q35" s="79"/>
+      <c r="R35" s="57"/>
       <c r="S35" s="15"/>
-      <c r="T35" s="90"/>
+      <c r="T35" s="74"/>
       <c r="U35" s="45"/>
       <c r="V35" s="45"/>
       <c r="W35" s="45"/>
@@ -58337,22 +58329,22 @@
       <c r="K36" s="96">
         <v>2025</v>
       </c>
-      <c r="L36" s="70" t="s">
+      <c r="L36" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="70" cm="1">
+      <c r="M36" s="15" cm="1">
         <f t="array" ref="M36">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L36,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1))))</f>
         <v>8</v>
       </c>
-      <c r="N36" s="97" cm="1">
+      <c r="N36" s="67" cm="1">
         <f t="array" ref="N36">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L36,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)))))</f>
         <v>4</v>
       </c>
-      <c r="O36" s="85">
-        <f>N36/(DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L36,$V$18:$V$29,0),1))</f>
+      <c r="O36" s="69">
+        <f t="shared" ref="O36:O47" si="6">N36/(DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L36,$V$18:$V$29,0),1))</f>
         <v>0.12903225806451613</v>
       </c>
-      <c r="P36" s="72" cm="1">
+      <c r="P36" s="38" cm="1">
         <f t="array" ref="P36">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L36,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L36,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>37446</v>
       </c>
@@ -58360,15 +58352,15 @@
         <f t="array" ref="Q36">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L36,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)))) - P36,"")</f>
         <v>36403.899999999994</v>
       </c>
-      <c r="R36" s="73" cm="1">
+      <c r="R36" s="57" cm="1">
         <f t="array" ref="R36">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L36,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>32.5</v>
       </c>
-      <c r="S36" s="72" cm="1">
+      <c r="S36" s="38" cm="1">
         <f t="array" ref="S36">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L36,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L36,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>2166.0300000000002</v>
       </c>
-      <c r="T36" s="87">
+      <c r="T36" s="71">
         <f>IFERROR(S36 / M36,"")</f>
         <v>270.75375000000003</v>
       </c>
@@ -58382,22 +58374,22 @@
       <c r="E37" s="12"/>
       <c r="I37" s="12"/>
       <c r="K37" s="96"/>
-      <c r="L37" s="75" t="s">
+      <c r="L37" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="M37" s="75" cm="1">
+      <c r="M37" s="45" cm="1">
         <f t="array" ref="M37">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L37,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1))))</f>
         <v>6</v>
       </c>
-      <c r="N37" s="98" cm="1">
+      <c r="N37" s="80" cm="1">
         <f t="array" ref="N37">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L37,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)))))</f>
         <v>5</v>
       </c>
-      <c r="O37" s="92">
-        <f>N37/(DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L37,$V$18:$V$29,0),1))</f>
+      <c r="O37" s="76">
+        <f t="shared" si="6"/>
         <v>0.17857142857142858</v>
       </c>
-      <c r="P37" s="79" cm="1">
+      <c r="P37" s="63" cm="1">
         <f t="array" ref="P37">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L37,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L37,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>34297</v>
       </c>
@@ -58405,16 +58397,16 @@
         <f t="array" ref="Q37">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L37,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)))) - P37,"")</f>
         <v>15748.099999999999</v>
       </c>
-      <c r="R37" s="80" cm="1">
+      <c r="R37" s="64" cm="1">
         <f t="array" ref="R37">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L37,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>19.166666666666668</v>
       </c>
-      <c r="S37" s="79" cm="1">
+      <c r="S37" s="63" cm="1">
         <f t="array" ref="S37">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L37,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L37,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>2472.02</v>
       </c>
-      <c r="T37" s="88">
-        <f t="shared" ref="T37:T47" si="5">IFERROR(S37 / M37,"")</f>
+      <c r="T37" s="72">
+        <f t="shared" ref="T37:T47" si="7">IFERROR(S37 / M37,"")</f>
         <v>412.00333333333333</v>
       </c>
       <c r="U37" s="45"/>
@@ -58426,22 +58418,22 @@
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
       <c r="K38" s="96"/>
-      <c r="L38" s="70" t="s">
+      <c r="L38" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="M38" s="70" cm="1">
+      <c r="M38" s="15" cm="1">
         <f t="array" ref="M38">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L38,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1))))</f>
         <v>11</v>
       </c>
-      <c r="N38" s="97" cm="1">
+      <c r="N38" s="67" cm="1">
         <f t="array" ref="N38">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L38,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)))))</f>
         <v>9</v>
       </c>
-      <c r="O38" s="85">
-        <f>N38/(DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L38,$V$18:$V$29,0),1))</f>
+      <c r="O38" s="69">
+        <f t="shared" si="6"/>
         <v>0.29032258064516131</v>
       </c>
-      <c r="P38" s="72" cm="1">
+      <c r="P38" s="38" cm="1">
         <f t="array" ref="P38">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L38,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L38,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>99617</v>
       </c>
@@ -58449,16 +58441,16 @@
         <f t="array" ref="Q38">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L38,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)))) - P38,"")</f>
         <v>57676.800000000017</v>
       </c>
-      <c r="R38" s="73" cm="1">
+      <c r="R38" s="57" cm="1">
         <f t="array" ref="R38">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L38,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>36.727272727272727</v>
       </c>
-      <c r="S38" s="72" cm="1">
+      <c r="S38" s="38" cm="1">
         <f t="array" ref="S38">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L38,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L38,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>3680.93</v>
       </c>
-      <c r="T38" s="87">
-        <f t="shared" si="5"/>
+      <c r="T38" s="71">
+        <f t="shared" si="7"/>
         <v>334.63</v>
       </c>
       <c r="U38" s="45"/>
@@ -58471,22 +58463,22 @@
       <c r="E39" s="12"/>
       <c r="I39" s="11"/>
       <c r="K39" s="96"/>
-      <c r="L39" s="75" t="s">
+      <c r="L39" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="M39" s="75" cm="1">
+      <c r="M39" s="45" cm="1">
         <f t="array" ref="M39">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L39,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1))))</f>
         <v>28</v>
       </c>
-      <c r="N39" s="98" cm="1">
+      <c r="N39" s="80" cm="1">
         <f t="array" ref="N39">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L39,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)))))</f>
         <v>18</v>
       </c>
-      <c r="O39" s="92">
-        <f>N39/(DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L39,$V$18:$V$29,0),1))</f>
+      <c r="O39" s="76">
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
-      <c r="P39" s="79" cm="1">
+      <c r="P39" s="63" cm="1">
         <f t="array" ref="P39">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L39,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L39,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>149794</v>
       </c>
@@ -58494,16 +58486,16 @@
         <f t="array" ref="Q39">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L39,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)))) - P39,"")</f>
         <v>120597.28999999998</v>
       </c>
-      <c r="R39" s="80" cm="1">
+      <c r="R39" s="64" cm="1">
         <f t="array" ref="R39">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L39,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>33.607142857142854</v>
       </c>
-      <c r="S39" s="79" cm="1">
+      <c r="S39" s="63" cm="1">
         <f t="array" ref="S39">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L39,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L39,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>7830.64</v>
       </c>
-      <c r="T39" s="88">
-        <f t="shared" si="5"/>
+      <c r="T39" s="72">
+        <f t="shared" si="7"/>
         <v>279.66571428571427</v>
       </c>
       <c r="U39" s="45"/>
@@ -58515,22 +58507,22 @@
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
       <c r="K40" s="96"/>
-      <c r="L40" s="70" t="s">
+      <c r="L40" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M40" s="70" cm="1">
+      <c r="M40" s="15" cm="1">
         <f t="array" ref="M40">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L40,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1))))</f>
         <v>20</v>
       </c>
-      <c r="N40" s="97" cm="1">
+      <c r="N40" s="67" cm="1">
         <f t="array" ref="N40">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L40,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)))))</f>
         <v>13</v>
       </c>
-      <c r="O40" s="85">
-        <f>N40/(DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L40,$V$18:$V$29,0),1))</f>
+      <c r="O40" s="69">
+        <f t="shared" si="6"/>
         <v>0.41935483870967744</v>
       </c>
-      <c r="P40" s="72" cm="1">
+      <c r="P40" s="38" cm="1">
         <f t="array" ref="P40">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L40,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L40,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>85786.4</v>
       </c>
@@ -58538,16 +58530,16 @@
         <f t="array" ref="Q40">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L40,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)))) - P40,"")</f>
         <v>98026.180000000022</v>
       </c>
-      <c r="R40" s="73" cm="1">
+      <c r="R40" s="57" cm="1">
         <f t="array" ref="R40">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L40,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>34.4</v>
       </c>
-      <c r="S40" s="72" cm="1">
+      <c r="S40" s="38" cm="1">
         <f t="array" ref="S40">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L40,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L40,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>5070.34</v>
       </c>
-      <c r="T40" s="87">
-        <f t="shared" si="5"/>
+      <c r="T40" s="71">
+        <f t="shared" si="7"/>
         <v>253.517</v>
       </c>
       <c r="U40" s="45"/>
@@ -58559,22 +58551,22 @@
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
       <c r="K41" s="96"/>
-      <c r="L41" s="75" t="s">
+      <c r="L41" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="75" cm="1">
+      <c r="M41" s="45" cm="1">
         <f t="array" ref="M41">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L41,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1))))</f>
         <v>28</v>
       </c>
-      <c r="N41" s="98" cm="1">
+      <c r="N41" s="80" cm="1">
         <f t="array" ref="N41">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L41,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)))))</f>
         <v>18</v>
       </c>
-      <c r="O41" s="92">
-        <f>N41/(DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L41,$V$18:$V$29,0),1))</f>
+      <c r="O41" s="76">
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
-      <c r="P41" s="79" cm="1">
+      <c r="P41" s="63" cm="1">
         <f t="array" ref="P41">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L41,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L41,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>116048</v>
       </c>
@@ -58582,16 +58574,16 @@
         <f t="array" ref="Q41">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L41,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)))) - P41,"")</f>
         <v>94414.15</v>
       </c>
-      <c r="R41" s="80" cm="1">
+      <c r="R41" s="64" cm="1">
         <f t="array" ref="R41">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L41,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>29.607142857142858</v>
       </c>
-      <c r="S41" s="79" cm="1">
+      <c r="S41" s="63" cm="1">
         <f t="array" ref="S41">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L41,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L41,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>6949.9599999999973</v>
       </c>
-      <c r="T41" s="88">
-        <f t="shared" si="5"/>
+      <c r="T41" s="72">
+        <f t="shared" si="7"/>
         <v>248.21285714285705</v>
       </c>
       <c r="U41" s="45"/>
@@ -58603,22 +58595,22 @@
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
       <c r="K42" s="96"/>
-      <c r="L42" s="70" t="s">
+      <c r="L42" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="M42" s="70" cm="1">
+      <c r="M42" s="15" cm="1">
         <f t="array" ref="M42">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L42,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1))))</f>
         <v>23</v>
       </c>
-      <c r="N42" s="97" cm="1">
+      <c r="N42" s="67" cm="1">
         <f t="array" ref="N42">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L42,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)))))</f>
         <v>16</v>
       </c>
-      <c r="O42" s="85">
-        <f>N42/(DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L42,$V$18:$V$29,0),1))</f>
+      <c r="O42" s="69">
+        <f t="shared" si="6"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="P42" s="72" cm="1">
+      <c r="P42" s="38" cm="1">
         <f t="array" ref="P42">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L42,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L42,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>92024</v>
       </c>
@@ -58626,16 +58618,16 @@
         <f t="array" ref="Q42">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L42,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)))) - P42,"")</f>
         <v>94877.700000000012</v>
       </c>
-      <c r="R42" s="73" cm="1">
+      <c r="R42" s="57" cm="1">
         <f t="array" ref="R42">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L42,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>26.434782608695652</v>
       </c>
-      <c r="S42" s="72" cm="1">
+      <c r="S42" s="38" cm="1">
         <f t="array" ref="S42">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L42,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L42,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>6976.4699999999993</v>
       </c>
-      <c r="T42" s="87">
-        <f t="shared" si="5"/>
+      <c r="T42" s="71">
+        <f t="shared" si="7"/>
         <v>303.32478260869561</v>
       </c>
       <c r="U42" s="45"/>
@@ -58647,22 +58639,22 @@
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
       <c r="K43" s="96"/>
-      <c r="L43" s="75" t="s">
+      <c r="L43" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="75" cm="1">
+      <c r="M43" s="45" cm="1">
         <f t="array" ref="M43">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L43,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1))))</f>
         <v>30</v>
       </c>
-      <c r="N43" s="98" cm="1">
+      <c r="N43" s="80" cm="1">
         <f t="array" ref="N43">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L43,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)))))</f>
         <v>17</v>
       </c>
-      <c r="O43" s="92">
-        <f>N43/(DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L43,$V$18:$V$29,0),1))</f>
+      <c r="O43" s="76">
+        <f t="shared" si="6"/>
         <v>0.54838709677419351</v>
       </c>
-      <c r="P43" s="79" cm="1">
+      <c r="P43" s="63" cm="1">
         <f t="array" ref="P43">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L43,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L43,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>114946</v>
       </c>
@@ -58670,16 +58662,16 @@
         <f t="array" ref="Q43">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L43,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)))) - P43,"")</f>
         <v>110041.67999999996</v>
       </c>
-      <c r="R43" s="80" cm="1">
+      <c r="R43" s="64" cm="1">
         <f t="array" ref="R43">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L43,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>29.2</v>
       </c>
-      <c r="S43" s="79" cm="1">
+      <c r="S43" s="63" cm="1">
         <f t="array" ref="S43">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L43,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L43,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>7468.89</v>
       </c>
-      <c r="T43" s="88">
-        <f t="shared" si="5"/>
+      <c r="T43" s="72">
+        <f t="shared" si="7"/>
         <v>248.96300000000002</v>
       </c>
       <c r="U43" s="45"/>
@@ -58691,22 +58683,22 @@
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
       <c r="K44" s="96"/>
-      <c r="L44" s="70" t="s">
+      <c r="L44" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M44" s="70" cm="1">
+      <c r="M44" s="15" cm="1">
         <f t="array" ref="M44">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L44,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1))))</f>
         <v>28</v>
       </c>
-      <c r="N44" s="97" cm="1">
+      <c r="N44" s="67" cm="1">
         <f t="array" ref="N44">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L44,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)))))</f>
         <v>19</v>
       </c>
-      <c r="O44" s="85">
-        <f>N44/(DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L44,$V$18:$V$29,0),1))</f>
+      <c r="O44" s="69">
+        <f t="shared" si="6"/>
         <v>0.6333333333333333</v>
       </c>
-      <c r="P44" s="72" cm="1">
+      <c r="P44" s="38" cm="1">
         <f t="array" ref="P44">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L44,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L44,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>127166.5</v>
       </c>
@@ -58714,16 +58706,16 @@
         <f t="array" ref="Q44">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L44,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)))) - P44,"")</f>
         <v>133761.12000000002</v>
       </c>
-      <c r="R44" s="73" cm="1">
+      <c r="R44" s="57" cm="1">
         <f t="array" ref="R44">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L44,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>29.035714285714285</v>
       </c>
-      <c r="S44" s="72" cm="1">
+      <c r="S44" s="38" cm="1">
         <f t="array" ref="S44">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L44,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L44,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>8529.36</v>
       </c>
-      <c r="T44" s="87">
-        <f t="shared" si="5"/>
+      <c r="T44" s="71">
+        <f t="shared" si="7"/>
         <v>304.62</v>
       </c>
       <c r="U44" s="45"/>
@@ -58735,22 +58727,22 @@
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
       <c r="K45" s="96"/>
-      <c r="L45" s="75" t="s">
+      <c r="L45" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="M45" s="75" cm="1">
+      <c r="M45" s="45" cm="1">
         <f t="array" ref="M45">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L45,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1))))</f>
         <v>33</v>
       </c>
-      <c r="N45" s="98" cm="1">
+      <c r="N45" s="80" cm="1">
         <f t="array" ref="N45">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L45,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)))))</f>
         <v>21</v>
       </c>
-      <c r="O45" s="92">
-        <f>N45/(DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L45,$V$18:$V$29,0),1))</f>
+      <c r="O45" s="76">
+        <f t="shared" si="6"/>
         <v>0.67741935483870963</v>
       </c>
-      <c r="P45" s="79" cm="1">
+      <c r="P45" s="63" cm="1">
         <f t="array" ref="P45">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L45,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L45,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>126594.5</v>
       </c>
@@ -58758,16 +58750,16 @@
         <f t="array" ref="Q45">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L45,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)))) - P45,"")</f>
         <v>137065.20000000001</v>
       </c>
-      <c r="R45" s="80" cm="1">
+      <c r="R45" s="64" cm="1">
         <f t="array" ref="R45">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L45,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>28.121212121212121</v>
       </c>
-      <c r="S45" s="79" cm="1">
+      <c r="S45" s="63" cm="1">
         <f t="array" ref="S45">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L45,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L45,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>8862.2399999999961</v>
       </c>
-      <c r="T45" s="88">
-        <f t="shared" si="5"/>
+      <c r="T45" s="72">
+        <f t="shared" si="7"/>
         <v>268.55272727272717</v>
       </c>
       <c r="U45" s="45"/>
@@ -58779,22 +58771,22 @@
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
       <c r="K46" s="96"/>
-      <c r="L46" s="70" t="s">
+      <c r="L46" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="M46" s="70" cm="1">
+      <c r="M46" s="15" cm="1">
         <f t="array" ref="M46">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L46,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1))))</f>
         <v>52</v>
       </c>
-      <c r="N46" s="97" cm="1">
+      <c r="N46" s="67" cm="1">
         <f t="array" ref="N46">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L46,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)))))</f>
         <v>16</v>
       </c>
-      <c r="O46" s="85">
-        <f>N46/(DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L46,$V$18:$V$29,0),1))</f>
+      <c r="O46" s="69">
+        <f t="shared" si="6"/>
         <v>0.53333333333333333</v>
       </c>
-      <c r="P46" s="72" cm="1">
+      <c r="P46" s="38" cm="1">
         <f t="array" ref="P46">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L46,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L46,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>268619.7</v>
       </c>
@@ -58802,16 +58794,16 @@
         <f t="array" ref="Q46">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L46,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)))) - P46,"")</f>
         <v>255439.09000000014</v>
       </c>
-      <c r="R46" s="73" cm="1">
+      <c r="R46" s="57" cm="1">
         <f t="array" ref="R46">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L46,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>34</v>
       </c>
-      <c r="S46" s="72" cm="1">
+      <c r="S46" s="38" cm="1">
         <f t="array" ref="S46">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L46,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L46,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>15916.289999999999</v>
       </c>
-      <c r="T46" s="87">
-        <f t="shared" si="5"/>
+      <c r="T46" s="71">
+        <f t="shared" si="7"/>
         <v>306.08249999999998</v>
       </c>
       <c r="U46" s="45"/>
@@ -58822,7 +58814,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
-      <c r="K47" s="57"/>
+      <c r="K47" s="97"/>
       <c r="L47" s="47" t="s">
         <v>39</v>
       </c>
@@ -58830,12 +58822,12 @@
         <f t="array" ref="M47">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L47,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L47,$V$18:$V$29,0) + 1,1))))</f>
         <v>29</v>
       </c>
-      <c r="N47" s="91" cm="1">
+      <c r="N47" s="75" cm="1">
         <f t="array" ref="N47">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$36,MATCH(L47,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$36,MATCH(L47,$V$18:$V$29,0) + 1,1)))))</f>
         <v>16</v>
       </c>
-      <c r="O47" s="93">
-        <f>N47/(DATE($K$36,MATCH(L47,$V$18:$V$29,0) + 1,1)-DATE($K$36,MATCH(L47,$V$18:$V$29,0),1))</f>
+      <c r="O47" s="77">
+        <f t="shared" si="6"/>
         <v>0.5161290322580645</v>
       </c>
       <c r="P47" s="49" cm="1">
@@ -58846,7 +58838,7 @@
         <f t="array" ref="Q47">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L47,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L47,$V$18:$V$29,0) + 1,1)))) - P47,"")</f>
         <v>118219.54999999996</v>
       </c>
-      <c r="R47" s="78" cm="1">
+      <c r="R47" s="62" cm="1">
         <f t="array" ref="R47">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L47,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L47,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>29.758620689655171</v>
       </c>
@@ -58854,8 +58846,8 @@
         <f t="array" ref="S47">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$36,MATCH(L47,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$36,MATCH(L47,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>8035.16</v>
       </c>
-      <c r="T47" s="89">
-        <f t="shared" si="5"/>
+      <c r="T47" s="73">
+        <f t="shared" si="7"/>
         <v>277.07448275862066</v>
       </c>
       <c r="U47" s="45"/>
@@ -58868,15 +58860,15 @@
       <c r="E48" s="12"/>
       <c r="K48" s="19"/>
       <c r="L48" s="15"/>
-      <c r="M48" s="105">
+      <c r="M48" s="87">
         <f>SUM(M36:M47)</f>
         <v>296</v>
       </c>
-      <c r="N48" s="81">
+      <c r="N48" s="65">
         <f>AVERAGE(N36:N47)</f>
         <v>14.333333333333334</v>
       </c>
-      <c r="O48" s="102">
+      <c r="O48" s="84">
         <f>AVERAGE(O36:O47)</f>
         <v>0.47016769073220682</v>
       </c>
@@ -58885,19 +58877,19 @@
         <v>1380014.8</v>
       </c>
       <c r="Q48" s="43">
-        <f t="shared" ref="Q48" si="6">SUM(Q36:Q47)</f>
+        <f t="shared" ref="Q48" si="8">SUM(Q36:Q47)</f>
         <v>1272270.7600000002</v>
       </c>
-      <c r="R48" s="81">
+      <c r="R48" s="65">
         <f>AVERAGE(R36:R47)</f>
         <v>30.2132129011252</v>
       </c>
       <c r="S48" s="43">
-        <f t="shared" ref="S48" si="7">AVERAGE(S36:S47)</f>
+        <f t="shared" ref="S48" si="9">AVERAGE(S36:S47)</f>
         <v>6996.5275000000001</v>
       </c>
       <c r="T48" s="43">
-        <f t="shared" ref="T48" si="8">AVERAGE(T36:T47)</f>
+        <f t="shared" ref="T48" si="10">AVERAGE(T36:T47)</f>
         <v>292.28334561682908</v>
       </c>
       <c r="U48" s="45"/>
@@ -58911,13 +58903,13 @@
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="94"/>
+      <c r="N49" s="67"/>
+      <c r="O49" s="78"/>
       <c r="P49" s="15"/>
-      <c r="Q49" s="95"/>
-      <c r="R49" s="68"/>
+      <c r="Q49" s="79"/>
+      <c r="R49" s="57"/>
       <c r="S49" s="15"/>
-      <c r="T49" s="90"/>
+      <c r="T49" s="74"/>
       <c r="U49" s="45"/>
       <c r="V49" s="45"/>
       <c r="W49" s="45"/>
@@ -58929,22 +58921,22 @@
       <c r="K50" s="96">
         <v>2026</v>
       </c>
-      <c r="L50" s="70" t="s">
+      <c r="L50" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="M50" s="70" cm="1">
+      <c r="M50" s="15" cm="1">
         <f t="array" ref="M50">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L50,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1))))</f>
         <v>23</v>
       </c>
-      <c r="N50" s="97" cm="1">
+      <c r="N50" s="67" cm="1">
         <f t="array" ref="N50">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L50,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)))))</f>
         <v>12</v>
       </c>
-      <c r="O50" s="85">
+      <c r="O50" s="69">
         <f>N50/(DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)-DATE($K$50,MATCH(L50,$V$18:$V$29,0),1))</f>
         <v>0.38709677419354838</v>
       </c>
-      <c r="P50" s="72" cm="1">
+      <c r="P50" s="38" cm="1">
         <f t="array" ref="P50">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L50,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L50,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>123622</v>
       </c>
@@ -58952,15 +58944,15 @@
         <f t="array" ref="Q50">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L50,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)))) - P50,"")</f>
         <v>110212.33999999991</v>
       </c>
-      <c r="R50" s="73" cm="1">
+      <c r="R50" s="57" cm="1">
         <f t="array" ref="R50">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L50,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>30.086956521739129</v>
       </c>
-      <c r="S50" s="72" cm="1">
+      <c r="S50" s="38" cm="1">
         <f t="array" ref="S50">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L50,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L50,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>8214.99</v>
       </c>
-      <c r="T50" s="87">
+      <c r="T50" s="71">
         <f>IFERROR(S50 / M50,"")</f>
         <v>357.17347826086956</v>
       </c>
@@ -58973,22 +58965,22 @@
       <c r="D51" s="12"/>
       <c r="E51" s="12"/>
       <c r="K51" s="96"/>
-      <c r="L51" s="75" t="s">
+      <c r="L51" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="M51" s="75" cm="1">
+      <c r="M51" s="45" cm="1">
         <f t="array" ref="M51">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L51,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1))))</f>
         <v>13</v>
       </c>
-      <c r="N51" s="98" cm="1">
+      <c r="N51" s="80" cm="1">
         <f t="array" ref="N51">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L51,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)))))</f>
         <v>11</v>
       </c>
-      <c r="O51" s="92">
+      <c r="O51" s="76">
         <f>N51/(DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)-DATE($K$50,MATCH(L51,$V$18:$V$29,0),1))</f>
         <v>0.39285714285714285</v>
       </c>
-      <c r="P51" s="79" cm="1">
+      <c r="P51" s="63" cm="1">
         <f t="array" ref="P51">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L51,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L51,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>53946.43</v>
       </c>
@@ -58996,16 +58988,16 @@
         <f t="array" ref="Q51">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L51,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)))) - P51,"")</f>
         <v>49899.460000000014</v>
       </c>
-      <c r="R51" s="80" cm="1">
+      <c r="R51" s="64" cm="1">
         <f t="array" ref="R51">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L51,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>31.384615384615383</v>
       </c>
-      <c r="S51" s="79" cm="1">
+      <c r="S51" s="63" cm="1">
         <f t="array" ref="S51">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L51,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L51,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>3516.6499999999996</v>
       </c>
-      <c r="T51" s="88">
-        <f t="shared" ref="T51:T54" si="9">IFERROR(S51 / M51,"")</f>
+      <c r="T51" s="72">
+        <f t="shared" ref="T51:T54" si="11">IFERROR(S51 / M51,"")</f>
         <v>270.51153846153841</v>
       </c>
       <c r="U51" s="45"/>
@@ -59017,22 +59009,22 @@
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
       <c r="K52" s="96"/>
-      <c r="L52" s="70" t="s">
+      <c r="L52" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="M52" s="70" cm="1">
+      <c r="M52" s="15" cm="1">
         <f t="array" ref="M52">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L52,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1))))</f>
         <v>15</v>
       </c>
-      <c r="N52" s="97" cm="1">
+      <c r="N52" s="67" cm="1">
         <f t="array" ref="N52">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L52,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)))))</f>
         <v>12</v>
       </c>
-      <c r="O52" s="85">
+      <c r="O52" s="69">
         <f>N52/(DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)-DATE($K$50,MATCH(L52,$V$18:$V$29,0),1))</f>
         <v>0.38709677419354838</v>
       </c>
-      <c r="P52" s="72" cm="1">
+      <c r="P52" s="38" cm="1">
         <f t="array" ref="P52">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L52,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L52,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>93264.5</v>
       </c>
@@ -59040,16 +59032,16 @@
         <f t="array" ref="Q52">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L52,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)))) - P52,"")</f>
         <v>47258.890000000014</v>
       </c>
-      <c r="R52" s="73" cm="1">
+      <c r="R52" s="57" cm="1">
         <f t="array" ref="R52">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L52,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>33.799999999999997</v>
       </c>
-      <c r="S52" s="72" cm="1">
+      <c r="S52" s="38" cm="1">
         <f t="array" ref="S52">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L52,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L52,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>4509.3900000000003</v>
       </c>
-      <c r="T52" s="87">
-        <f t="shared" si="9"/>
+      <c r="T52" s="71">
+        <f t="shared" si="11"/>
         <v>300.62600000000003</v>
       </c>
       <c r="U52" s="45"/>
@@ -59061,22 +59053,22 @@
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
       <c r="K53" s="96"/>
-      <c r="L53" s="75" t="s">
+      <c r="L53" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="M53" s="75" cm="1">
+      <c r="M53" s="45" cm="1">
         <f t="array" ref="M53">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L53,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1))))</f>
         <v>10</v>
       </c>
-      <c r="N53" s="98" cm="1">
+      <c r="N53" s="80" cm="1">
         <f t="array" ref="N53">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L53,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)))))</f>
         <v>10</v>
       </c>
-      <c r="O53" s="92">
+      <c r="O53" s="76">
         <f>N53/(DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)-DATE($K$50,MATCH(L53,$V$18:$V$29,0),1))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="P53" s="79" cm="1">
+      <c r="P53" s="63" cm="1">
         <f t="array" ref="P53">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[precio], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L53,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)))) - SUM(_xlfn._xlws.FILTER(factVentas[anticipo], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L53,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>66743</v>
       </c>
@@ -59084,16 +59076,16 @@
         <f t="array" ref="Q53">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L53,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)))) - P53,"")</f>
         <v>45705.47</v>
       </c>
-      <c r="R53" s="80" cm="1">
+      <c r="R53" s="64" cm="1">
         <f t="array" ref="R53">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L53,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>34.200000000000003</v>
       </c>
-      <c r="S53" s="79" cm="1">
+      <c r="S53" s="63" cm="1">
         <f t="array" ref="S53">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L53,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L53,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>3771.77</v>
       </c>
-      <c r="T53" s="88">
-        <f t="shared" si="9"/>
+      <c r="T53" s="72">
+        <f t="shared" si="11"/>
         <v>377.17700000000002</v>
       </c>
       <c r="U53" s="45"/>
@@ -59104,7 +59096,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
-      <c r="K54" s="57"/>
+      <c r="K54" s="97"/>
       <c r="L54" s="39" t="s">
         <v>32</v>
       </c>
@@ -59112,11 +59104,11 @@
         <f t="array" ref="M54">COUNT(_xlfn._xlws.FILTER(factVentas[folio], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L54,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L54,$V$18:$V$29,0) + 1,1))))</f>
         <v>16</v>
       </c>
-      <c r="N54" s="82" cm="1">
+      <c r="N54" s="66" cm="1">
         <f t="array" ref="N54">COUNT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(factVentas[fecha], (factVentas[fecha]&gt;=DATE($K$50,MATCH(L54,$V$18:$V$29,0),1))*(factVentas[fecha]&lt;DATE($K$50,MATCH(L54,$V$18:$V$29,0) + 1,1)))))</f>
         <v>13</v>
       </c>
-      <c r="O54" s="84">
+      <c r="O54" s="68">
         <f>N54/(DATE($K$50,MATCH(L54,$V$18:$V$29,0) + 1,1)-DATE($K$50,MATCH(L54,$V$18:$V$29,0),1))</f>
         <v>0.41935483870967744</v>
       </c>
@@ -59128,7 +59120,7 @@
         <f t="array" ref="Q54">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[total], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L54,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L54,$V$18:$V$29,0) + 1,1)))) - P54,"")</f>
         <v>63968.719999999972</v>
       </c>
-      <c r="R54" s="77" cm="1">
+      <c r="R54" s="61" cm="1">
         <f t="array" ref="R54">IFERROR(AVERAGE(_xlfn._xlws.FILTER(factVentas[plazos], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L54,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L54,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>33.6875</v>
       </c>
@@ -59136,8 +59128,8 @@
         <f t="array" ref="S54">IFERROR(SUM(_xlfn._xlws.FILTER(factVentas[semanal], (factVentas[fecha] &gt;= DATE($K$50,MATCH(L54,$V$18:$V$29,0),1)) * (factVentas[fecha] &lt; DATE($K$50,MATCH(L54,$V$18:$V$29,0) + 1,1)))),"")</f>
         <v>5346.68</v>
       </c>
-      <c r="T54" s="86">
-        <f t="shared" si="9"/>
+      <c r="T54" s="70">
+        <f t="shared" si="11"/>
         <v>334.16750000000002</v>
       </c>
       <c r="U54" s="45"/>
@@ -59150,35 +59142,35 @@
       <c r="E55" s="12"/>
       <c r="K55" s="52"/>
       <c r="L55" s="15"/>
-      <c r="M55" s="106">
+      <c r="M55" s="88">
         <f>SUM(M50:M54)</f>
         <v>77</v>
       </c>
-      <c r="N55" s="100">
+      <c r="N55" s="82">
         <f>AVERAGE(N50:N54)</f>
         <v>11.6</v>
       </c>
-      <c r="O55" s="101">
+      <c r="O55" s="83">
         <f>AVERAGE(O50:O54)</f>
         <v>0.38394777265745011</v>
       </c>
-      <c r="P55" s="99">
+      <c r="P55" s="81">
         <f>SUM(P50:P54)</f>
         <v>442366.43</v>
       </c>
-      <c r="Q55" s="99">
+      <c r="Q55" s="81">
         <f>SUM(Q50:Q54)</f>
         <v>317044.87999999989</v>
       </c>
-      <c r="R55" s="100">
+      <c r="R55" s="82">
         <f>AVERAGE(R50:R54)</f>
         <v>32.6318143812709</v>
       </c>
-      <c r="S55" s="99">
+      <c r="S55" s="81">
         <f>AVERAGE(S50:S54)</f>
         <v>5071.8959999999997</v>
       </c>
-      <c r="T55" s="99">
+      <c r="T55" s="81">
         <f>AVERAGE(T50:T54)</f>
         <v>327.93110334448158</v>
       </c>
@@ -59210,35 +59202,35 @@
       <c r="E57" s="12"/>
       <c r="K57" s="45"/>
       <c r="L57" s="45"/>
-      <c r="M57" s="107">
+      <c r="M57" s="89">
         <f>SUM(M20,M34,M48,M55)</f>
         <v>449</v>
       </c>
-      <c r="N57" s="108">
+      <c r="N57" s="90">
         <f>AVERAGE(N55,N48,N34,N20)</f>
         <v>8.1916666666666664</v>
       </c>
-      <c r="O57" s="109">
+      <c r="O57" s="91">
         <f>AVERAGE(O55,O48,O34,O20)</f>
         <v>0.26927135750481135</v>
       </c>
-      <c r="P57" s="110">
+      <c r="P57" s="92">
         <f>SUM(P55,P48,P34,P20)</f>
         <v>2270361.23</v>
       </c>
-      <c r="Q57" s="110">
+      <c r="Q57" s="92">
         <f>SUM(Q55,Q48,Q34,Q20)</f>
         <v>1906422.9200000002</v>
       </c>
-      <c r="R57" s="108">
+      <c r="R57" s="90">
         <f>AVERAGE(R55,R48,R34,R20)</f>
         <v>28.80658339460981</v>
       </c>
-      <c r="S57" s="110">
+      <c r="S57" s="92">
         <f>AVERAGE(S55,S48,S34,S20)</f>
         <v>3886.185375</v>
       </c>
-      <c r="T57" s="110">
+      <c r="T57" s="92">
         <f>AVERAGE(T55,T48,T34,T20)</f>
         <v>351.01371055714242</v>
       </c>
@@ -59503,11 +59495,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D12:F13"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="R16:T16"/>
+    <mergeCell ref="K50:K54"/>
     <mergeCell ref="K22:K33"/>
     <mergeCell ref="K36:K47"/>
     <mergeCell ref="B3:D6"/>
@@ -59515,7 +59507,7 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H29:I29"/>
-    <mergeCell ref="K50:K54"/>
+    <mergeCell ref="D12:F13"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
